--- a/docs/EIDE-VUNG-MAN-HINH.xlsx
+++ b/docs/EIDE-VUNG-MAN-HINH.xlsx
@@ -1208,13 +1208,13 @@
         <is>
           <t>• Khối CÒN THIẾU đầu bảng, nói rõ thiếu gì và ai trả lời được
 • Từng bước: mục tiêu · năng lực · fact trích dẫn · điều kiện xong
-• Quyết định cổng G1 + nút DUYỆT ngay trên màn
+• Quyết định cổng G1: ai quyết, quy tắc nào, lúc nào (duyệt ở vùng trao đổi)
 • Ước lượng chi phí so với hạn ngày</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Duyệt kế hoạch; Từ chối kèm lý do; Lập lại</t>
+          <t>Mở vùng trao đổi để duyệt; Lập lại</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
